--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/241339</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,8 +906,17 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83336984</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,52 +794,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83336984</v>
+        <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>106813</v>
+        <v>111565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>219716</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 22145, Vg</t>
+          <t>Hönsatorp, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415597</v>
+        <v>415613</v>
       </c>
       <c r="R3" t="n">
-        <v>6500470</v>
+        <v>6500455</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,24 +866,19 @@
           <t>Forshem</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1BB73327-BC38-4A9B-B82A-53CB25E44F82</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-10-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-10-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Inventerat av Johanna Johansson</t>
+          <t>Flera i bankslänt på södra sidan. Rikligt i ängsmarken utanför vägområdet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,23 +890,153 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bankslänt</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson, Anna Bergqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135707437</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83336984</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>VGL Träd ID: 22145, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>415597</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6500470</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Götene</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Forshem</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1BB73327-BC38-4A9B-B82A-53CB25E44F82</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-10-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-10-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventerat av Johanna Johansson</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Lars Sjögren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Lars Sjögren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83336984</t>
         </is>
@@ -916,6 +1046,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,52 +794,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83336984</v>
+        <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>106813</v>
+        <v>111570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>219716</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 22145, Vg</t>
+          <t>Hönsatorp, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415597</v>
+        <v>415613</v>
       </c>
       <c r="R3" t="n">
-        <v>6500470</v>
+        <v>6500455</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,24 +866,19 @@
           <t>Forshem</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1BB73327-BC38-4A9B-B82A-53CB25E44F82</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-10-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-10-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Inventerat av Johanna Johansson</t>
+          <t>Flera i bankslänt på södra sidan. Rikligt i ängsmarken utanför vägområdet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,23 +890,153 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bankslänt</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson, Anna Bergqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135707437</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83336984</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>VGL Träd ID: 22145, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>415597</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6500470</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Götene</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Forshem</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1BB73327-BC38-4A9B-B82A-53CB25E44F82</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-10-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-10-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventerat av Johanna Johansson</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Lars Sjögren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Lars Sjögren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83336984</t>
         </is>
@@ -916,6 +1046,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>111570</v>
+        <v>111572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>111572</v>
+        <v>111595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>111595</v>
+        <v>111597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>111597</v>
+        <v>111598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>111598</v>
+        <v>111599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>111599</v>
+        <v>111605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21378-2026 artfynd.xlsx
+++ b/artfynd/A 21378-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135707437</v>
       </c>
       <c r="B3" t="n">
-        <v>111605</v>
+        <v>111606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
